--- a/Results/df_mnd_miro_pla_sequential_trial_gap_unweighted.xlsx
+++ b/Results/df_mnd_miro_pla_sequential_trial_gap_unweighted.xlsx
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="E2" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="F2" t="n">
-        <v>0.53</v>
+        <v>0.45</v>
       </c>
       <c r="G2" t="n">
-        <v>3.705479726777605e-08</v>
+        <v>4.967891734922242e-11</v>
       </c>
     </row>
     <row r="3">
@@ -502,16 +502,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="E3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F3" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="G3" t="n">
-        <v>8.996623501789437e-09</v>
+        <v>1.983811198185388e-11</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="G4" t="n">
-        <v>6.326527738685615e-09</v>
+        <v>1.582492183236103e-11</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.07</v>
+        <v>0.18</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05585781537496716</v>
+        <v>0.002220009727194793</v>
       </c>
     </row>
   </sheetData>
